--- a/output/pdf_financials_xlsx/MTH.xlsx
+++ b/output/pdf_financials_xlsx/MTH.xlsx
@@ -1240,31 +1240,31 @@
         <v>-0.130468</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.42633</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="17">
@@ -1280,7 +1280,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.967008</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.05</v>
@@ -1509,10 +1509,10 @@
         <v>-0.501702</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.483504</v>
+        <v>-0.483504</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.224645</v>
+        <v>-1.224645</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.308019</v>
@@ -1524,31 +1524,31 @@
         <v>-0.130468</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.42633</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="21">
@@ -1674,10 +1674,10 @@
         <v>-0.501702</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.483504</v>
+        <v>-0.483504</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.224645</v>
+        <v>-1.224645</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.308019</v>
@@ -1689,31 +1689,31 @@
         <v>-0.130468</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.42633</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="24">
@@ -1853,10 +1853,10 @@
         <v>12.54255</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>16.1168</v>
+        <v>-16.1168</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20.41075</v>
+        <v>-20.41075</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>19.7386</v>
+        <v>-19.7386</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1945,31 +1945,31 @@
         <v>-0.130468</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.42633</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="28">
@@ -2055,31 +2055,31 @@
         <v>-0.130468</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.42633</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="30">
@@ -2182,7 +2182,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>4.256605187099081</v>
@@ -2197,31 +2197,31 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.463038</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0.235141</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.404936</v>
+        <v>2.132648</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0.472936</v>
@@ -5977,7 +5977,7 @@
         <v>-0.060701</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-0.9829560000000001</v>
@@ -10430,7 +10430,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -17534,7 +17538,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -41434,13 +41442,13 @@
         </is>
       </c>
       <c r="O353" s="5" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="P353" s="5" t="n">
-        <v>0.506365</v>
+        <v>-0.506365</v>
       </c>
       <c r="Q353" s="5" t="n">
-        <v>0.188271</v>
+        <v>-0.188271</v>
       </c>
       <c r="R353" t="inlineStr">
         <is>
@@ -41448,10 +41456,10 @@
         </is>
       </c>
       <c r="S353" s="5" t="n">
-        <v>0.453394</v>
+        <v>-0.453394</v>
       </c>
       <c r="T353" s="5" t="n">
-        <v>0.910253</v>
+        <v>-0.910253</v>
       </c>
     </row>
     <row r="354">
@@ -41726,7 +41734,7 @@
         </is>
       </c>
       <c r="Q356" s="5" t="n">
-        <v>0.9829560000000001</v>
+        <v>-0.9829560000000001</v>
       </c>
       <c r="R356" s="5" t="n">
         <v>-0.42633</v>
@@ -43518,13 +43526,13 @@
         </is>
       </c>
       <c r="O375" s="5" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="P375" s="5" t="n">
-        <v>0.50381</v>
+        <v>-0.50381</v>
       </c>
       <c r="Q375" s="5" t="n">
-        <v>0.183348</v>
+        <v>-0.183348</v>
       </c>
       <c r="R375" t="inlineStr">
         <is>
@@ -44359,10 +44367,10 @@
         </is>
       </c>
       <c r="N384" s="5" t="n">
-        <v>0.060701</v>
+        <v>-0.060701</v>
       </c>
       <c r="O384" s="5" t="n">
-        <v>0.25752</v>
+        <v>-0.25752</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -45092,10 +45100,10 @@
         </is>
       </c>
       <c r="G392" s="5" t="n">
-        <v>0.483504</v>
+        <v>-0.483504</v>
       </c>
       <c r="H392" s="5" t="n">
-        <v>1.224645</v>
+        <v>-1.224645</v>
       </c>
       <c r="I392" s="5" t="n">
         <v>-0.308019</v>
@@ -45107,10 +45115,10 @@
         <v>-0.130468</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>0.394772</v>
+        <v>-0.394772</v>
       </c>
       <c r="M392" s="5" t="n">
-        <v>0.178034</v>
+        <v>-0.178034</v>
       </c>
       <c r="N392" t="inlineStr">
         <is>
@@ -47689,10 +47697,10 @@
         </is>
       </c>
       <c r="H419" s="5" t="n">
-        <v>1.224645</v>
+        <v>-1.224645</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>0.308019</v>
+        <v>-0.308019</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MTH.xlsx
+++ b/output/pdf_financials_xlsx/MTH.xlsx
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004077</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001707</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1032,19 +1032,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002555</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.004923</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.003273</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000267</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
     </row>
     <row r="13">
@@ -1927,10 +1927,10 @@
         <v>-0.010029</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.501702</v>
+        <v>-0.505779</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.483504</v>
+        <v>0.481797</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1.174645</v>
@@ -1957,19 +1957,19 @@
         <v>-0.25752</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.506365</v>
+        <v>-0.50892</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.9829560000000001</v>
+        <v>-0.987879</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.42633</v>
+        <v>-0.429603</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.453394</v>
+        <v>-0.453661</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.910253</v>
+        <v>-0.913843</v>
       </c>
     </row>
     <row r="28">
@@ -2037,10 +2037,10 @@
         <v>-0.010029</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.501702</v>
+        <v>-0.505779</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.484202</v>
+        <v>0.482495</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.17609</v>
@@ -2067,19 +2067,19 @@
         <v>-0.25752</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.506365</v>
+        <v>-0.50892</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.9829560000000001</v>
+        <v>-0.987879</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.42633</v>
+        <v>-0.429603</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.453394</v>
+        <v>-0.453661</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.910253</v>
+        <v>-0.913843</v>
       </c>
     </row>
     <row r="30">
@@ -2325,46 +2325,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.6319709999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.238698</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.252904</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00276</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.023988</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002513</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002041</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.265554</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00179</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002618</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.321675</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.709981</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.026256</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.010039</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.00459</v>
@@ -2435,46 +2435,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.6319709999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.238698</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.252904</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.00276</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.023988</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002513</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002041</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.265554</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00179</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.002618</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.321675</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.400123</v>
+        <v>1.110104</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.196218</v>
+        <v>0.222474</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.021521</v>
+        <v>0.03156</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.00459</v>
@@ -3095,43 +3095,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6319709999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.245955</v>
+        <v>0.007257</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.311721</v>
+        <v>0.058817</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.091269</v>
+        <v>0.088509</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.059942</v>
+        <v>0.035954</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.038023</v>
+        <v>0.03551</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016159</v>
+        <v>0.014118</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.311232</v>
+        <v>0.045678</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.04058</v>
+        <v>0.03879</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.041071</v>
+        <v>0.038453</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.508292</v>
+        <v>0.186617</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.779646</v>
+        <v>0.069665</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.045021</v>
+        <v>0.018765</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -42410,7 +42410,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -42988,7 +42988,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -44796,7 +44796,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -45750,7 +45750,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -48064,7 +48064,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -49812,7 +49812,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">

--- a/output/pdf_financials_xlsx/MTH.xlsx
+++ b/output/pdf_financials_xlsx/MTH.xlsx
@@ -6604,19 +6604,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013497</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013497</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012592</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020246</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>0.002292</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7907,19 +7907,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013497</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013497</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012592</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020246</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002292</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.143057</v>
+        <v>-0.156554</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.405028</v>
+        <v>-0.41762</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.446954</v>
+        <v>-0.4672</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.030298</v>
+        <v>-0.03259</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.064746</v>
@@ -21106,7 +21106,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -23196,7 +23200,11 @@
           <t>Private placement 7</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -34818,7 +34826,11 @@
           <t>Disposal (purchase) of equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -35006,7 +35018,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -36624,7 +36640,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37870,7 +37890,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E316" s="5" t="n">
         <v>-0.013497</v>
       </c>
